--- a/artfynd/A 34527-2025 artfynd.xlsx
+++ b/artfynd/A 34527-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439532</v>
       </c>
       <c r="B3" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136439534</v>
       </c>
       <c r="B4" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136439533</v>
       </c>
       <c r="B5" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34527-2025 artfynd.xlsx
+++ b/artfynd/A 34527-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439532</v>
       </c>
       <c r="B3" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136439534</v>
       </c>
       <c r="B4" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136439533</v>
       </c>
       <c r="B5" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34527-2025 artfynd.xlsx
+++ b/artfynd/A 34527-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439532</v>
       </c>
       <c r="B3" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136439534</v>
       </c>
       <c r="B4" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136439533</v>
       </c>
       <c r="B5" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34527-2025 artfynd.xlsx
+++ b/artfynd/A 34527-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439532</v>
       </c>
       <c r="B3" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136439534</v>
       </c>
       <c r="B4" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136439533</v>
       </c>
       <c r="B5" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34527-2025 artfynd.xlsx
+++ b/artfynd/A 34527-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439532</v>
       </c>
       <c r="B3" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136439534</v>
       </c>
       <c r="B4" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136439533</v>
       </c>
       <c r="B5" t="n">
-        <v>102801</v>
+        <v>102807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34527-2025 artfynd.xlsx
+++ b/artfynd/A 34527-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439532</v>
       </c>
       <c r="B3" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136439534</v>
       </c>
       <c r="B4" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136439533</v>
       </c>
       <c r="B5" t="n">
-        <v>102807</v>
+        <v>102809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34527-2025 artfynd.xlsx
+++ b/artfynd/A 34527-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136439532</v>
       </c>
       <c r="B3" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136439534</v>
       </c>
       <c r="B4" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>136439533</v>
       </c>
       <c r="B5" t="n">
-        <v>102809</v>
+        <v>102810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
